--- a/consultations.xlsx
+++ b/consultations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,90 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:08:23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test User</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>+977 9800000000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kathmandu</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>birth-chart</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Testing server</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:09:32</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Verified User</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>+1 555-0199</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1995-05-15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>career</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Verification test</t>
         </is>
       </c>
     </row>
